--- a/Config/Excel/GameConfig/EmitterEffectConfig.xlsx
+++ b/Config/Excel/GameConfig/EmitterEffectConfig.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BuffGroupConfig" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuffGroupConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1028,7 +1028,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1147,7 +1152,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>目标属性：1=CooldownMs，2=Range，3=WhiteDamage，4=BaseDamage</t>
+          <t>目标属性：1=CooldownMs，2=Range，3=BaseDamage，4=AttackRatio</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1172,8 +1177,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4"/>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>70001</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -1181,19 +1185,19 @@
           <t>CD减少50%</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>0.5</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
@@ -1203,39 +1207,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5"/>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>70002</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>伤害+50%</t>
-        </is>
-      </c>
-      <c r="D5">
+          <t>基础伤害+50%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>1.5</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>发射器白值伤害倍率乘以1.5</t>
+          <t>发射器基础伤害乘以1.5</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6"/>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>70003</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -1243,19 +1245,19 @@
           <t>射程+30%</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>1.3</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
@@ -1265,8 +1267,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7"/>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>71001</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -1274,19 +1275,19 @@
           <t>击退1米</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>61101</v>
       </c>
       <c r="I7" t="inlineStr">
@@ -1296,8 +1297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8"/>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>71002</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -1305,19 +1305,19 @@
           <t>冻结0.5秒</t>
         </is>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>2</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>61102</v>
       </c>
       <c r="I8" t="inlineStr">
@@ -1327,8 +1327,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9"/>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>71003</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -1336,19 +1335,19 @@
           <t>减速30%</t>
         </is>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>61103</v>
       </c>
       <c r="I9" t="inlineStr">
@@ -1358,8 +1357,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10"/>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>71004</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -1367,19 +1365,19 @@
           <t>毒伤DOT</t>
         </is>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>2</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>61104</v>
       </c>
       <c r="I10" t="inlineStr">
@@ -1389,5 +1387,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>